--- a/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
+++ b/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source Application</t>
+          <t>Source Configuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KFZCQAMBH71P21137Z5QGG04</t>
+          <t>h_01KHB1PZ6VJ232MEPB6DDFKTHJ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KFZCQAMBH71P21137Z5QGG04</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB1PZ6VJ232MEPB6DDFKTHJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application Provisioning Configuration</t>
+          <t>Provisioning</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KFZCWZ4MMSSWW2GKAWEK5ZJK</t>
+          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KFZCWZ4MMSSWW2GKAWEK5ZJK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
     </row>

--- a/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
+++ b/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,51 +727,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Notification Rule</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGJBQTWYRM77C2WVP8E</t>
+          <t>h_01KHB7SXSRYYW1HY90MSTKPKT6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG2E4KGJBQTWYRM77C2WVP8E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB7SXSRYYW1HY90MSTKPKT6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Assignment Rules</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KG2C9SH8E7ZHD7CDPX9ZWRNY</t>
+          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG2C9SH8E7ZHD7CDPX9ZWRNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Define PII Attribute</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,29 +793,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KG2CNKQEEHJD2XAZ9GV147N5</t>
+          <t>h_01KHB7SXSRBV3PYRAR1HPX5MGZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG2CNKQEEHJD2XAZ9GV147N5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB7SXSRBV3PYRAR1HPX5MGZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Define PII Attribute</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01KG2CNKQEEHJD2XAZ9GV147N5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG2CNKQEEHJD2XAZ9GV147N5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Define PII Attribute</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGHCD65P9P0PY3KY9QD</t>
+          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG2E4KGHCD65P9P0PY3KY9QD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KG2E4KGHCD65P9P0PY3KY9QD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG2E4KGHCD65P9P0PY3KY9QD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,54 +913,76 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Email Notification Settings</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01KG4JSB4MRYSX92ACQDWVBQ2T</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KG4JSB4MRYSX92ACQDWVBQ2T</t>
         </is>

--- a/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
+++ b/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHB7SXSRYYW1HY90MSTKPKT6</t>
+          <t>h_01KHBC8P4ZC05SGZV72J835H58</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB7SXSRYYW1HY90MSTKPKT6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHBC8P4ZC05SGZV72J835H58</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHB7SXSRBV3PYRAR1HPX5MGZ</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHB7SXSRBV3PYRAR1HPX5MGZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>

--- a/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
+++ b/site/Entra-SCIM-Application-Outbound-Provisioning-Integration-Guide/headings.xlsx
@@ -947,12 +947,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
